--- a/AutomacaoAcompanhamentoDiario/Base_Chegada_Unilever.xlsx
+++ b/AutomacaoAcompanhamentoDiario/Base_Chegada_Unilever.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="22">
   <si>
     <t>ID</t>
   </si>
@@ -22,73 +22,64 @@
     <t>TIPO</t>
   </si>
   <si>
+    <t>PLACA</t>
+  </si>
+  <si>
     <t>MOTORISTA</t>
   </si>
   <si>
+    <t>DOCK_DATA</t>
+  </si>
+  <si>
     <t>HORA_CHEGADA</t>
   </si>
   <si>
     <t>CHECKIN_CD</t>
   </si>
   <si>
-    <t>DOCK_DATA</t>
-  </si>
-  <si>
-    <t>DME</t>
+    <t>PROG. ENTREGA</t>
   </si>
   <si>
     <t>CHEGADA_CLIENTE</t>
   </si>
   <si>
-    <t>PROGRAMAÇÃO. COLETA</t>
-  </si>
-  <si>
-    <t>PROGRAMAÇÃO. ENTREGA</t>
-  </si>
-  <si>
     <t>ORIGEM</t>
   </si>
   <si>
     <t>DESTINO</t>
   </si>
   <si>
-    <t xml:space="preserve"> 1020521812 /  98147314 / 98147315</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1020522187 /  98148163 / 98148164</t>
-  </si>
-  <si>
-    <t>COLETA</t>
-  </si>
-  <si>
-    <t>GILMAR FEHMBERGER</t>
-  </si>
-  <si>
-    <t>05/04/2026 12:24</t>
-  </si>
-  <si>
-    <t>05/04/2026 07:03</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>05/04/2026 12:00</t>
-  </si>
-  <si>
-    <t>05/04/2026 13:00</t>
+    <t xml:space="preserve"> 1020975999 / 98370983</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1020976001 / 98371179</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1020987482 / 98376714</t>
+  </si>
+  <si>
+    <t>ENTREGA</t>
   </si>
   <si>
     <t>---</t>
   </si>
   <si>
-    <t>06/04/2026 08:00</t>
-  </si>
-  <si>
-    <t>INDAIATUBA - SP</t>
-  </si>
-  <si>
-    <t>LOUVEIRA - SP</t>
+    <t>26/06/2026 06:00</t>
+  </si>
+  <si>
+    <t>26/06/2026 07:00</t>
+  </si>
+  <si>
+    <t>24/06/2026 12:27</t>
+  </si>
+  <si>
+    <t>SERRA - ES</t>
+  </si>
+  <si>
+    <t>COLOMBO - PR</t>
+  </si>
+  <si>
+    <t>SIMOES FILHO - BA</t>
   </si>
 </sst>
 </file>
@@ -446,10 +437,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,81 +474,92 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
       <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
